--- a/cet4/result/15_修仙校园_最强丹道少女/15_修仙校园_最强丹道少女_学习版.xlsx
+++ b/cet4/result/15_修仙校园_最强丹道少女/15_修仙校园_最强丹道少女_学习版.xlsx
@@ -397,759 +397,703 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D49"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>countryside</v>
       </c>
       <c r="B2" t="str">
-        <v>countryside</v>
+        <v>/ˈkʌntrisaɪd/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>农村</v>
       </c>
-      <c r="D2" t="str">
-        <v>countryside(农村)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>breeze</v>
       </c>
       <c r="B3" t="str">
-        <v>breeze</v>
+        <v>/briːz/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./vi.</v>
+      </c>
+      <c r="D3" t="str">
         <v>微风</v>
       </c>
-      <c r="D3" t="str">
-        <v>breeze(微风)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>body</v>
       </c>
       <c r="B4" t="str">
-        <v>body</v>
+        <v>/ˈbɑːdi/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D4" t="str">
         <v>身体</v>
       </c>
-      <c r="D4" t="str">
-        <v>body(身体)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>say</v>
       </c>
       <c r="B5" t="str">
-        <v>say</v>
+        <v>/seɪ/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D5" t="str">
         <v>说</v>
       </c>
-      <c r="D5" t="str">
-        <v>say(说)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>severe</v>
       </c>
       <c r="B6" t="str">
-        <v>severe</v>
+        <v>/sɪˈvɪr/</v>
       </c>
       <c r="C6" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>严峻的</v>
       </c>
-      <c r="D6" t="str">
-        <v>severe(严峻的)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>sincere</v>
       </c>
       <c r="B7" t="str">
-        <v>sincere</v>
+        <v>/sɪnˈsɪr/</v>
       </c>
       <c r="C7" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D7" t="str">
         <v>真诚的</v>
       </c>
-      <c r="D7" t="str">
-        <v>sincere(真诚的)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>inspect</v>
       </c>
       <c r="B8" t="str">
-        <v>inspect</v>
+        <v>/ɪnˈspekt/</v>
       </c>
       <c r="C8" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D8" t="str">
         <v>检查</v>
       </c>
-      <c r="D8" t="str">
-        <v>inspect(检查)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>terrific</v>
       </c>
       <c r="B9" t="str">
-        <v>terrific</v>
+        <v>/təˈrɪfɪk/</v>
       </c>
       <c r="C9" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>极好的</v>
       </c>
-      <c r="D9" t="str">
-        <v>terrific(极好的)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>clap</v>
       </c>
       <c r="B10" t="str">
-        <v>clap</v>
+        <v>/klæp/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D10" t="str">
         <v>鼓掌</v>
       </c>
-      <c r="D10" t="str">
-        <v>clap(鼓掌)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>arrangement</v>
       </c>
       <c r="B11" t="str">
-        <v>arrangement</v>
+        <v>/əˈreɪndʒmənt/</v>
       </c>
       <c r="C11" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>安排</v>
       </c>
-      <c r="D11" t="str">
-        <v>arrangement(安排)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>clarify</v>
       </c>
       <c r="B12" t="str">
-        <v>clarify</v>
+        <v>/ˈklærəfaɪ/</v>
       </c>
       <c r="C12" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D12" t="str">
         <v>澄清</v>
       </c>
-      <c r="D12" t="str">
-        <v>clarify(澄清)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>democracy</v>
       </c>
       <c r="B13" t="str">
-        <v>democracy</v>
+        <v>/dɪˈmɑːkrəsi/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>民主</v>
       </c>
-      <c r="D13" t="str">
-        <v>democracy(民主)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>achievement</v>
       </c>
       <c r="B14" t="str">
-        <v>achievement</v>
+        <v>/əˈtʃiːvmənt/</v>
       </c>
       <c r="C14" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>成就</v>
       </c>
-      <c r="D14" t="str">
-        <v>achievement(成就)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>attend</v>
       </c>
       <c r="B15" t="str">
-        <v>attend</v>
+        <v>/əˈtend/</v>
       </c>
       <c r="C15" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D15" t="str">
         <v>出席</v>
       </c>
-      <c r="D15" t="str">
-        <v>attend(出席)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>various</v>
       </c>
       <c r="B16" t="str">
-        <v>various</v>
+        <v>/ˈveriəs,ˈværiəs/</v>
       </c>
       <c r="C16" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D16" t="str">
         <v>各种各样的</v>
       </c>
-      <c r="D16" t="str">
-        <v>various(各种各样的)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>careful</v>
       </c>
       <c r="B17" t="str">
-        <v>careful</v>
+        <v>/ˈkerfl/</v>
       </c>
       <c r="C17" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D17" t="str">
         <v>仔细的</v>
       </c>
-      <c r="D17" t="str">
-        <v>careful(仔细的)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>nice</v>
       </c>
       <c r="B18" t="str">
-        <v>nice</v>
+        <v>/naɪs/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D18" t="str">
         <v>美好的</v>
       </c>
-      <c r="D18" t="str">
-        <v>nice(美好的)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>dye</v>
       </c>
       <c r="B19" t="str">
-        <v>dye</v>
+        <v>/daɪ/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D19" t="str">
         <v>染料</v>
       </c>
-      <c r="D19" t="str">
-        <v>dye(染料)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>beauty</v>
       </c>
       <c r="B20" t="str">
-        <v>beauty</v>
+        <v>/ˈbjuːti/</v>
       </c>
       <c r="C20" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>美</v>
       </c>
-      <c r="D20" t="str">
-        <v>beauty(美)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>whoever</v>
       </c>
       <c r="B21" t="str">
-        <v>whoever</v>
+        <v>/huːˈevər/</v>
       </c>
       <c r="C21" t="str">
+        <v>n./pron.</v>
+      </c>
+      <c r="D21" t="str">
         <v>无论谁</v>
       </c>
-      <c r="D21" t="str">
-        <v>whoever(无论谁)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>soldier</v>
       </c>
       <c r="B22" t="str">
-        <v>severe</v>
+        <v>/ˈsoʊldʒər/</v>
       </c>
       <c r="C22" t="str">
-        <v>严峻的</v>
+        <v>n./vi.</v>
       </c>
       <c r="D22" t="str">
-        <v>severe(严峻的)📢</v>
+        <v>士兵</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>which</v>
       </c>
       <c r="B23" t="str">
-        <v>soldier</v>
+        <v>/wɪtʃ/</v>
       </c>
       <c r="C23" t="str">
-        <v>士兵</v>
+        <v>n./adj./pron.</v>
       </c>
       <c r="D23" t="str">
-        <v>soldier(士兵)📢</v>
+        <v>哪个</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>may</v>
       </c>
       <c r="B24" t="str">
-        <v>which</v>
+        <v>/meɪ/</v>
       </c>
       <c r="C24" t="str">
-        <v>哪个</v>
+        <v>aux.</v>
       </c>
       <c r="D24" t="str">
-        <v>which(哪个)📢</v>
+        <v>可能</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>discovery</v>
       </c>
       <c r="B25" t="str">
-        <v>may</v>
+        <v>/dɪˈskʌvəri/</v>
       </c>
       <c r="C25" t="str">
-        <v>可能</v>
+        <v>n.</v>
       </c>
       <c r="D25" t="str">
-        <v>may(可能)📢</v>
+        <v>发现</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>destroy</v>
       </c>
       <c r="B26" t="str">
-        <v>discovery</v>
+        <v>/dɪˈstrɔɪ/</v>
       </c>
       <c r="C26" t="str">
-        <v>发现</v>
+        <v>vt.</v>
       </c>
       <c r="D26" t="str">
-        <v>discovery(发现)📢</v>
+        <v>破坏</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>retain</v>
       </c>
       <c r="B27" t="str">
-        <v>destroy</v>
+        <v>/rɪˈteɪn/</v>
       </c>
       <c r="C27" t="str">
-        <v>破坏</v>
+        <v>vt.</v>
       </c>
       <c r="D27" t="str">
-        <v>destroy(破坏)📢</v>
+        <v>保持</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>recovery</v>
       </c>
       <c r="B28" t="str">
-        <v>retain</v>
+        <v>/rɪˈkʌvəri/</v>
       </c>
       <c r="C28" t="str">
-        <v>保持</v>
+        <v>n.</v>
       </c>
       <c r="D28" t="str">
-        <v>retain(保持)📢</v>
+        <v>恢复</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>power</v>
       </c>
       <c r="B29" t="str">
-        <v>achievement</v>
+        <v>/ˈpaʊər/</v>
       </c>
       <c r="C29" t="str">
-        <v>成就</v>
+        <v>n./vt.</v>
       </c>
       <c r="D29" t="str">
-        <v>achievement(成就)📢</v>
+        <v>力量</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>inquiry</v>
       </c>
       <c r="B30" t="str">
-        <v>recovery</v>
+        <v>/ɪnˈkwaɪəri; ˈɪnkwəri/</v>
       </c>
       <c r="C30" t="str">
-        <v>恢复</v>
+        <v>n.</v>
       </c>
       <c r="D30" t="str">
-        <v>recovery(恢复)📢</v>
+        <v>调查</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>reliable</v>
       </c>
       <c r="B31" t="str">
-        <v>power</v>
+        <v>/rɪˈlaɪəbl/</v>
       </c>
       <c r="C31" t="str">
-        <v>力量</v>
+        <v>n./adj.</v>
       </c>
       <c r="D31" t="str">
-        <v>power(力量)📢</v>
+        <v>可靠的</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>rub</v>
       </c>
       <c r="B32" t="str">
-        <v>inquiry</v>
+        <v>/rʌb/</v>
       </c>
       <c r="C32" t="str">
-        <v>调查</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D32" t="str">
-        <v>inquiry(调查)📢</v>
+        <v>摩擦</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>embrace</v>
       </c>
       <c r="B33" t="str">
-        <v>reliable</v>
+        <v>/ɪmˈbreɪs/</v>
       </c>
       <c r="C33" t="str">
-        <v>可靠的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D33" t="str">
-        <v>reliable(可靠的)📢</v>
+        <v>拥抱</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>laughter</v>
       </c>
       <c r="B34" t="str">
-        <v>rub</v>
+        <v>/ˈlæftər/</v>
       </c>
       <c r="C34" t="str">
-        <v>摩擦</v>
+        <v>n.</v>
       </c>
       <c r="D34" t="str">
-        <v>rub(摩擦)📢</v>
+        <v>笑声</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>continuous</v>
       </c>
       <c r="B35" t="str">
-        <v>embrace</v>
+        <v>/kənˈtɪnjuəs/</v>
       </c>
       <c r="C35" t="str">
-        <v>拥抱</v>
+        <v>adj.</v>
       </c>
       <c r="D35" t="str">
-        <v>embrace(拥抱)📢</v>
+        <v>连续的</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>crime</v>
       </c>
       <c r="B36" t="str">
-        <v>laughter</v>
+        <v>/kraɪm/</v>
       </c>
       <c r="C36" t="str">
-        <v>笑声</v>
+        <v>n./vt.</v>
       </c>
       <c r="D36" t="str">
-        <v>laughter(笑声)📢</v>
+        <v>罪行</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>horror</v>
       </c>
       <c r="B37" t="str">
-        <v>continuous</v>
+        <v>/ˈhɔːrər/</v>
       </c>
       <c r="C37" t="str">
-        <v>连续的</v>
+        <v>n.</v>
       </c>
       <c r="D37" t="str">
-        <v>continuous(连续的)📢</v>
+        <v>恐惧</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>broad</v>
       </c>
       <c r="B38" t="str">
-        <v>crime</v>
+        <v>/brɔːd/</v>
       </c>
       <c r="C38" t="str">
-        <v>罪行</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D38" t="str">
-        <v>crime(罪行)📢</v>
+        <v>宽的</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>tolerate</v>
       </c>
       <c r="B39" t="str">
-        <v>horror</v>
+        <v>/ˈtɑːləreɪt/</v>
       </c>
       <c r="C39" t="str">
-        <v>恐惧</v>
+        <v>vt.</v>
       </c>
       <c r="D39" t="str">
-        <v>horror(恐惧)📢</v>
+        <v>忍受</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>weaken</v>
       </c>
       <c r="B40" t="str">
-        <v>broad</v>
+        <v>/ˈwiːkən/</v>
       </c>
       <c r="C40" t="str">
-        <v>宽的</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D40" t="str">
-        <v>broad(宽的)📢</v>
+        <v>减弱</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>afraid</v>
       </c>
       <c r="B41" t="str">
-        <v>tolerate</v>
+        <v>/əˈfreɪd/</v>
       </c>
       <c r="C41" t="str">
-        <v>忍受</v>
+        <v>adj.</v>
       </c>
       <c r="D41" t="str">
-        <v>tolerate(忍受)📢</v>
+        <v>害怕</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>haste</v>
       </c>
       <c r="B42" t="str">
-        <v>weaken</v>
+        <v>/heɪst/</v>
       </c>
       <c r="C42" t="str">
-        <v>减弱</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D42" t="str">
-        <v>weaken(减弱)📢</v>
+        <v>匆忙</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>skirt</v>
       </c>
       <c r="B43" t="str">
-        <v>afraid</v>
+        <v>/skɜːrt/</v>
       </c>
       <c r="C43" t="str">
-        <v>害怕</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D43" t="str">
-        <v>afraid(害怕)📢</v>
+        <v>裙子</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>fasten</v>
       </c>
       <c r="B44" t="str">
-        <v>haste</v>
+        <v>/ˈfæsn/</v>
       </c>
       <c r="C44" t="str">
-        <v>匆忙</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D44" t="str">
-        <v>haste(匆忙)📢</v>
+        <v>固定</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>other</v>
       </c>
       <c r="B45" t="str">
-        <v>skirt</v>
+        <v>/ˈʌðər/</v>
       </c>
       <c r="C45" t="str">
-        <v>裙子</v>
+        <v>n./adj./pron.</v>
       </c>
       <c r="D45" t="str">
-        <v>skirt(裙子)📢</v>
+        <v>其他</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>saw</v>
       </c>
       <c r="B46" t="str">
-        <v>fasten</v>
+        <v>/sɔː/</v>
       </c>
       <c r="C46" t="str">
-        <v>固定</v>
+        <v>n./v.</v>
       </c>
       <c r="D46" t="str">
-        <v>fasten(固定)📢</v>
+        <v>锯</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>spy</v>
       </c>
       <c r="B47" t="str">
-        <v>other</v>
+        <v>/spaɪ/</v>
       </c>
       <c r="C47" t="str">
-        <v>其他</v>
+        <v>n./v.</v>
       </c>
       <c r="D47" t="str">
-        <v>other(其他)📢</v>
+        <v>间谍</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>African</v>
       </c>
       <c r="B48" t="str">
-        <v>saw</v>
+        <v>/ˈæfrɪkən/</v>
       </c>
       <c r="C48" t="str">
-        <v>锯</v>
+        <v>n./adj.</v>
       </c>
       <c r="D48" t="str">
-        <v>saw(锯)📢</v>
+        <v>非洲的</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>worker</v>
       </c>
       <c r="B49" t="str">
-        <v>spy</v>
+        <v>/ˈwɜːrkər/</v>
       </c>
       <c r="C49" t="str">
-        <v>间谍</v>
+        <v>n.</v>
       </c>
       <c r="D49" t="str">
-        <v>spy(间谍)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>African</v>
-      </c>
-      <c r="C50" t="str">
-        <v>非洲的</v>
-      </c>
-      <c r="D50" t="str">
-        <v>African(非洲的)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>worker</v>
-      </c>
-      <c r="C51" t="str">
         <v>工人</v>
-      </c>
-      <c r="D51" t="str">
-        <v>worker(工人)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>power</v>
-      </c>
-      <c r="C52" t="str">
-        <v>力量</v>
-      </c>
-      <c r="D52" t="str">
-        <v>power(力量)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>countryside</v>
-      </c>
-      <c r="C53" t="str">
-        <v>农村</v>
-      </c>
-      <c r="D53" t="str">
-        <v>countryside(农村)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D53"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D49"/>
   </ignoredErrors>
 </worksheet>
 </file>